--- a/artfynd/A 62065-2024 artfynd.xlsx
+++ b/artfynd/A 62065-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>94289094</v>
       </c>
       <c r="B2" t="n">
-        <v>57587</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -740,10 +735,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>323507.2129140939</v>
+        <v>323507</v>
       </c>
       <c r="R2" t="n">
-        <v>6473486.303915928</v>
+        <v>6473487</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -773,19 +768,9 @@
           <t>2021-05-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-05-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -817,15 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94289134</v>
+        <v>94289111</v>
       </c>
       <c r="B3" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,21 +813,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>208242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -860,11 +840,15 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -878,10 +862,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>323507.2129140939</v>
+        <v>323507</v>
       </c>
       <c r="R3" t="n">
-        <v>6473486.303915928</v>
+        <v>6473487</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -911,19 +895,9 @@
           <t>2021-05-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-05-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -955,15 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94289111</v>
+        <v>94289134</v>
       </c>
       <c r="B4" t="n">
-        <v>57585</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,21 +940,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208242</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -998,15 +967,11 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1020,10 +985,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>323507.2129140939</v>
+        <v>323507</v>
       </c>
       <c r="R4" t="n">
-        <v>6473486.303915928</v>
+        <v>6473487</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1053,19 +1018,9 @@
           <t>2021-05-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-05-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 62065-2024 artfynd.xlsx
+++ b/artfynd/A 62065-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94289094</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -926,6 +936,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94289111</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1049,8 +1064,18 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94289134</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>